--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>spec.md, plan.md, tasks.md exist; plan.md resolves every open question; tasks.md is granular enough to execute; stakeholder signed off.</t>
+          <t>spec.md exists and clearly states the user story, what's in scope, what's out of scope, and the exact numbers that count as a successful test run.</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>spec.md, plan.md, tasks.md exist; plan.md resolves every open question; tasks.md is granular enough to execute; stakeholder signed off.</t>
+          <t>plan.md exists and every open design question has a real decision written down, not left blank.</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>spec.md, plan.md, tasks.md exist; plan.md resolves every open question; tasks.md is granular enough to execute; stakeholder signed off.</t>
+          <t>tasks.md exists and breaks every PBI into small tasks specific enough that nobody has to ask 'what do you mean' before starting one.</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>spec.md, plan.md, tasks.md exist; plan.md resolves every open question; tasks.md is granular enough to execute; stakeholder signed off.</t>
+          <t>Someone has actually read spec.md, plan.md, and tasks.md and said 'yes, build this' - silence doesn't count as approval.</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Repo installs cleanly; lint passes; all schemas parse a sample JSON fixture each.</t>
+          <t>Running the install command works with no errors, and the linter (ruff) reports zero problems.</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Repo installs cleanly; lint passes; all schemas parse a sample JSON fixture each.</t>
+          <t>.env.example lists all three required keys (OpenRouter, Gemini, Groq) with no real secrets inside it, and the real .env file is excluded from git.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Repo installs cleanly; lint passes; all schemas parse a sample JSON fixture each.</t>
+          <t>Every data shape from plan.md (EvalRun, LLMCallResult, etc.) exists as a schema, and each one can successfully load a small hand-written sample without crashing.</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Renderer produces a correctly filled prompt for every variant/test-case pair; missing-variable case caught with a readable error.</t>
+          <t>A real example JSON file exists with multiple prompt variants and test cases, and it loads successfully into the EvalRun schema with no errors.</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Renderer produces a correctly filled prompt for every variant/test-case pair; missing-variable case caught with a readable error.</t>
+          <t>Given one prompt variant and one test case, the renderer returns the template with every {blank} correctly replaced by the real value.</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Renderer produces a correctly filled prompt for every variant/test-case pair; missing-variable case caught with a readable error.</t>
+          <t>Tests exist and pass proving every variant/test-case combo renders correctly, and that a missing variable produces a clear, readable error instead of a raw crash.</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>All N x M x K calls execute concurrently; every result is a valid LLMCallResult; a forced single-call failure doesn't abort the batch.</t>
+          <t>One function can send a prompt to any of the three providers (OpenRouter, Gemini, Groq) just by changing the model name string.</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>All N x M x K calls execute concurrently; every result is a valid LLMCallResult; a forced single-call failure doesn't abort the batch.</t>
+          <t>Multiple calls fire at the same time instead of one-by-one, and the number running at once never goes above the concurrency limit.</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>All N x M x K calls execute concurrently; every result is a valid LLMCallResult; a forced single-call failure doesn't abort the batch.</t>
+          <t>Every successful call's result includes the real input token count, output token count, and how many milliseconds it took.</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>All N x M x K calls execute concurrently; every result is a valid LLMCallResult; a forced single-call failure doesn't abort the batch.</t>
+          <t>A temporary failure (like a rate limit) gets retried automatically with increasing wait times; if it still fails after retries, the result's error field is filled in instead of the program crashing.</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Every LLMCallResult gets a valid JudgeResult; a malformed judge response never raises past the retry/fallback path.</t>
+          <t>The judge prompt template exists and includes the rubric, the candidate answer, and clear instructions to return only JSON with a score and reasoning.</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Every LLMCallResult gets a valid JudgeResult; a malformed judge response never raises past the retry/fallback path.</t>
+          <t>A real judge call returns a score from 1-5 plus reasoning text, and it loads correctly into the JudgeResult schema.</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Every LLMCallResult gets a valid JudgeResult; a malformed judge response never raises past the retry/fallback path.</t>
+          <t>If the judge's response isn't valid JSON, the program asks again once; if it still fails, the result gets a score of 0 and a 'parse failure' reason instead of crashing.</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Every LLMCallResult gets a valid JudgeResult; a malformed judge response never raises past the retry/fallback path.</t>
+          <t>Tests exist and pass for three cases: a valid JSON response, a broken JSON response, and a JSON response wrapped in markdown formatting.</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>One end-to-end run produces a RunReport with a ranked table and a recommended_variant_id + rationale naming concrete reasons.</t>
+          <t>Each prompt variant gets one combined score built from its average quality, cost, and speed, using the weighting formula from plan.md.</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>One end-to-end run produces a RunReport with a ranked table and a recommended_variant_id + rationale naming concrete reasons.</t>
+          <t>The program picks exactly one winning variant and writes a plain-English reason for why each other variant scored lower (quality, cost, or speed).</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>One end-to-end run produces a RunReport with a ranked table and a recommended_variant_id + rationale naming concrete reasons.</t>
+          <t>Running a report prints a readable ranked table in the terminal and also saves the full results to a JSON file.</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Fresh clone + README-only setup produces a working run; no unhandled exceptions in the E2E pass.</t>
+          <t>Running the tool for real - 3 prompt variants x 5 test cases against all three providers - produces a complete report with no crashes.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Fresh clone + README-only setup produces a working run; no unhandled exceptions in the E2E pass.</t>
+          <t>README.md lets someone install the tool, set up their API keys, and run their first evaluation using only the instructions in that file.</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Fresh clone + README-only setup produces a working run; no unhandled exceptions in the E2E pass.</t>
+          <t>Every issue found during the real end-to-end run in T8.1 has been fixed and re-tested.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>cost_usd on a known token count matches a hand calculation; unknown models fall back to cost_usd=None.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>cost_usd on a known token count matches a hand calculation; unknown models fall back to cost_usd=None.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>A simulated timeout or mid-run failure still yields a RunReport containing every result that did complete.</t>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>A simulated timeout or mid-run failure still yields a RunReport containing every result that did complete.</t>
+          <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>
       </c>
     </row>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E37)</f>
+        <f>SUM(E10:E39)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E37)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E39)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E37)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E39)</f>
         <v/>
       </c>
     </row>
@@ -1445,82 +1445,82 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>PBI-8 End-to-End Testing &amp; Docs</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>T8.1</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Full E2E run on one real task through all three providers</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PBI-9 CLI Orchestrator</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>T9.1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Build cli.py entry point: prompteval run &lt;input.json&gt; [--judge-model] [--concurrency] [--timeout] [--format]</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>1.5</v>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>Running the tool for real - 3 prompt variants x 5 test cases against all three providers - produces a complete report with no crashes.</t>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Thu 6 Aug</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Typing 'prompteval run &lt;file&gt;' in a real terminal works as an actual command, and passing --judge-model/--concurrency/--timeout/--format changes its behavior instead of being ignored.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>PBI-8 End-to-End Testing &amp; Docs</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>T8.2</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Write README.md</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PBI-9 CLI Orchestrator</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>T9.2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Wire pipeline: load input -&gt; render -&gt; execute -&gt; judge -&gt; score -&gt; report</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>README.md lets someone install the tool, set up their API keys, and run their first evaluation using only the instructions in that file.</t>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Thu 6 Aug</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>One single command runs the entire tool start to finish -- load the file, render prompts, call the AI, judge the answers, rank them, and save a report -- with no separate scripts needed.</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>T8.3</t>
+          <t>T8.1</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Final bug fixes/polish from E2E run</t>
+          <t>Full E2E run on one real task through all three providers</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
@@ -1560,94 +1560,94 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
+          <t>Running the tool for real - 3 prompt variants x 5 test cases against all three providers - produces a complete report with no crashes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>PBI-8 End-to-End Testing &amp; Docs</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>T8.2</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Write README.md</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>README.md lets someone install the tool, set up their API keys, and run their first evaluation using only the instructions in that file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>PBI-8 End-to-End Testing &amp; Docs</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>T8.3</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Final bug fixes/polish from E2E run</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
           <t>Every issue found during the real end-to-end run in T8.1 has been fixed and re-tested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>T5.2</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Compute cost_usd per call/variant</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E36" s="8" t="n">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
@@ -1710,15 +1710,95 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>T7.1</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Confirm partial failures never drop completed results</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
           <t>Unscheduled (if time remains)</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -1555,7 +1555,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E39)</f>
+        <f>SUM(E10:E40)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E39)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E40)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E39)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E40)</f>
         <v/>
       </c>
     </row>
@@ -1645,42 +1645,42 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PBI-10 Interactive Setup Wizard</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>T10.1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Add `prompteval init` -- asks for task name, prompt variants, test cases, and rubric in the terminal, then saves a real input file</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tue 4 Aug</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Answering the terminal questions produces a real input file that `prompteval run` can load and execute with no manual edits needed.</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
@@ -1720,14 +1720,14 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E38" s="8" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
@@ -1799,6 +1799,46 @@
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E40)</f>
+        <f>SUM(E10:E41)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E40)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E41)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E40)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E41)</f>
         <v/>
       </c>
     </row>
@@ -1685,42 +1685,42 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PBI-11 AI-Generated Quickstart</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>T11.1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Add `prompteval quickstart` -- AI generates a random task (or uses one you type) plus 5 test cases; user types 3 prompts; the evaluation runs immediately with no separate file/run step</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tue 4 Aug</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Running the command with no pre-made file, answering only the task and 3 prompts, produces a real ranked report -- proven live with a genuine AI-generated task, 5 generated test cases, and a real evaluation run.</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E38" s="8" t="n">
@@ -1760,14 +1760,14 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E40" s="8" t="n">
@@ -1839,6 +1839,46 @@
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E41)</f>
+        <f>SUM(E10:E42)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E41)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E42)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E41)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E42)</f>
         <v/>
       </c>
     </row>
@@ -1725,42 +1725,42 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PBI-11 AI-Generated Quickstart</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>T11.2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Make quickstart the default when `prompteval` is run with no subcommand (or only flags)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tue 4 Aug</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Typing plain 'prompteval' (or 'prompteval --judge-model x') with no subcommand at all starts the quickstart flow directly; 'prompteval run &lt;file&gt;' and 'prompteval init' still work exactly as before.</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E40" s="8" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
@@ -1879,6 +1879,46 @@
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E42)</f>
+        <f>SUM(E10:E43)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E42)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E43)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E42)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E43)</f>
         <v/>
       </c>
     </row>
@@ -1765,42 +1765,42 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="n">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PBI-12 Friendly Help &amp; Onboarding</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>T12.1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Add `prompteval /help` (also `help`/`-h`/`--help`) -- a warm, example-filled guide instead of argparse's terse default; add a clear message instead of a crash when no API key is configured at all</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Wed 5 Aug</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Typing 'prompteval /help' in a real terminal (PowerShell, confirmed) prints a full walkthrough. Running any real command with zero API keys set prints a clear fix-it message and exits cleanly instead of crashing deep inside a network call.</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E40" s="8" t="n">
@@ -1840,14 +1840,14 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E42" s="8" t="n">
@@ -1919,6 +1919,46 @@
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E43)</f>
+        <f>SUM(E10:E44)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E43)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E44)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E43)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E44)</f>
         <v/>
       </c>
     </row>
@@ -1805,42 +1805,42 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PBI-13 Single-Prompt Improvement Mode</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>T13.1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Add `prompteval improve` -- asks for context + ONE prompt, AI generates 3 realistic scenarios and actually runs the prompt against them, then a judge model writes plain-English feedback (not a 1-5 score) on how to improve it</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Wed 5 Aug</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Running the real command with a real prompt produces genuinely specific, actionable written feedback based on real outputs, and saves it to a real markdown file -- confirmed live, not just mocked.</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
@@ -1880,14 +1880,14 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E42" s="8" t="n">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
@@ -1959,6 +1959,46 @@
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E44)</f>
+        <f>SUM(E10:E46)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E44)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E46)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E44)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E46)</f>
         <v/>
       </c>
     </row>
@@ -1845,89 +1845,89 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PBI-14 Double-Click Run Button</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>T14.1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Add 'Run PromtEval.cmd' -- double-click launches quickstart with no venv activation and no flags needed, stays open afterward so results are readable</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Wed 5 Aug</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Double-clicking (simulated via a real piped PowerShell invocation) launches the tool, completes a real run, and the window stays open on 'Press any key to continue' instead of vanishing.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>T5.2</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Compute cost_usd per call/variant</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PBI-14 Double-Click Run Button</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>T14.2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bug fix found via the run button: a stray BOM character injected by PowerShell's stdin piping made a 'blank' wizard answer look non-empty, silently skipping AI task generation</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Wed 5 Aug</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Re-running the same real scenario after the fix shows a proper AI-generated task name instead of an empty/garbled one; added a regression test using a real BOM character so this can't silently regress.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -1960,14 +1960,14 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E44" s="8" t="n">
@@ -1990,15 +1990,95 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>T7.1</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Confirm partial failures never drop completed results</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
           <t>Unscheduled (if time remains)</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -1822,11 +1822,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Add `prompteval improve` -- asks for context + ONE prompt, AI generates 3 realistic scenarios and actually runs the prompt against them, then a judge model writes plain-English feedback (not a 1-5 score) on how to improve it</t>
+          <t>Add `prompteval improve` -- asks for ONE prompt only (no separate context question), AI generates 3 realistic scenarios from the prompt's own wording and actually runs it against them, then returns a strict score (1-5) + reasoning + a rewritten, improved prompt (structured JSON, not prose)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Running the real command with a real prompt produces genuinely specific, actionable written feedback based on real outputs, and saves it to a real markdown file -- confirmed live, not just mocked.</t>
+          <t>Running the real command with just a prompt (no context asked) produces a real 1-5 score, reasoning grounded in real outputs, and a genuinely rewritten prompt, saved to a real markdown file -- confirmed live.</t>
         </is>
       </c>
     </row>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E46)</f>
+        <f>SUM(E10:E47)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E46)</f>
+        <f>SUMIF(B10:B37,"Must",E10:E47)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E46)</f>
+        <f>SUMIF(B10:B37,"Stretch",E10:E47)</f>
         <v/>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PBI-15 Change Default to Improve</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>T15.1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Change the no-subcommand default (bare 'prompteval' and the double-click .cmd) from quickstart to improve, since single-prompt scoring turned out to be the actually wanted default flow</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Wed 5 Aug</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bare 'prompteval' and double-clicking 'Run PromtEval.cmd' both now go straight into the improve flow (asks for one prompt, returns score + rewrite) -- confirmed with two separate live runs. 'quickstart'/'init'/'run' still work unchanged when named explicitly.</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E44" s="8" t="n">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E46" s="8" t="n">
@@ -2079,6 +2079,46 @@
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B37,"Must",E10:E47)</f>
+        <f>SUMIF(B10:B47,"Must",E10:E47)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B37,"Stretch",E10:E47)</f>
+        <f>SUMIF(B10:B47,"Stretch",E10:E47)</f>
         <v/>
       </c>
     </row>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E47)</f>
+        <f>SUM(E10:E49)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B47,"Must",E10:E47)</f>
+        <f>SUMIF(B10:B49,"Must",E10:E49)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B47,"Stretch",E10:E47)</f>
+        <f>SUMIF(B10:B49,"Stretch",E10:E49)</f>
         <v/>
       </c>
     </row>
@@ -1965,89 +1965,89 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PBI-16 Interactive Terminal Menu</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>T16.1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Add an arrow-key menu (questionary) shown when no subcommand is given, replacing the direct default -- lets the user pick Improve/Quickstart/Init/Run/Help/Exit without knowing a command name; existing flags are preserved and applied to whatever gets picked</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Thu 6 Aug</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Running bare 'prompteval' shows a real arrow-key menu; picking an option runs that exact flow. 12 dedicated tests cover every choice including Ctrl+C/Esc and looping back after Help.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PBI-16 Interactive Terminal Menu</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>T16.2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bug found via live testing in Git Bash: questionary's arrow-key menu crashes outright in terminals without a real Windows console buffer (Git Bash/mintty, confirmed live) -- added a graceful numbered-list fallback via input() instead of a raw crash</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>T5.2</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Compute cost_usd per call/variant</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Thu 6 Aug</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Re-ran the exact same real scenario in Git Bash after the fix: the fallback numbered menu renders, accepts a real answer, and a full menu-to-improve run completes end-to-end with a real score + rewrite -- confirmed live, not just mocked.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E46" s="8" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -2080,14 +2080,14 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
@@ -2110,15 +2110,95 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>T7.1</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Confirm partial failures never drop completed results</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
           <t>Unscheduled (if time remains)</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E49)</f>
+        <f>SUM(E10:E50)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B49,"Must",E10:E49)</f>
+        <f>SUMIF(B10:B50,"Must",E10:E50)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B49,"Stretch",E10:E49)</f>
+        <f>SUMIF(B10:B50,"Stretch",E10:E50)</f>
         <v/>
       </c>
     </row>
@@ -2045,42 +2045,42 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="n">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PBI-16 Interactive Terminal Menu</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>T16.3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>User feedback: menu's Help option just repeated the generic /help install guide, not useful in context; 'Build a reusable input file'/'Run an existing input file' choices were unclear. Reworded all 4 main choices to be self-explanatory and added a menu-specific MENU_HELP_TEXT explaining exactly what each option does</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Fri 7 Aug</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Thu 6 Aug</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Selecting Help from the real menu (confirmed live) now explains each option in plain terms with a concrete example, instead of repeating the install/API-key guide.</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
@@ -2120,14 +2120,14 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E48" s="8" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
@@ -2199,6 +2199,46 @@
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E50)</f>
+        <f>SUM(E10:E51)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B50,"Must",E10:E50)</f>
+        <f>SUMIF(B10:B51,"Must",E10:E51)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B50,"Stretch",E10:E50)</f>
+        <f>SUMIF(B10:B51,"Stretch",E10:E51)</f>
         <v/>
       </c>
     </row>
@@ -2085,42 +2085,42 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>PBI-5 Cost &amp; Latency Calculation</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Build pricing table ($ per input/output token)</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PBI-17 Anthropic/Claude Provider Support</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>T17.1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Add ANTHROPIC_API_KEY to the 'is any key configured?' check, .env.example, and /help + no-key message -- LiteLLM already routes anthropic/claude-* model strings with no other code changes needed</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Fri 7 Aug</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>A real Anthropic key was added and litellm successfully authenticated a live request to Claude (proven -- reached a genuine billing error, not an auth error). Actual generation is blocked by the account having a zero credit balance, a billing issue on the user's Anthropic account, not a code gap; the wiring itself is confirmed correct.</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Compute cost_usd per call/variant</t>
+          <t>Build pricing table ($ per input/output token)</t>
         </is>
       </c>
       <c r="E48" s="8" t="n">
@@ -2160,14 +2160,14 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
+          <t>A pricing table exists listing $ per input token and $ per output token for every in-scope model.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>PBI-7 Error Handling &amp; Reliability</t>
+          <t>PBI-5 Cost &amp; Latency Calculation</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Confirm partial failures never drop completed results</t>
+          <t>Compute cost_usd per call/variant</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Unscheduled (if time remains)</t>
+          <t>Fri 7 Aug</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+          <t>Given a call's real token counts, the calculated dollar cost matches what you'd get doing the multiplication by hand.</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Add explicit per-provider timeout handling</t>
+          <t>Confirm partial failures never drop completed results</t>
         </is>
       </c>
       <c r="E50" s="8" t="n">
@@ -2239,6 +2239,46 @@
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>If some calls in a batch fail, the finished ones are still included in the final report - nothing gets thrown away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>PBI-7 Error Handling &amp; Reliability</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Stretch</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>T7.2</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Add explicit per-provider timeout handling</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Unscheduled (if time remains)</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>A call that hangs past the timeout limit gets cancelled and recorded as a timeout error, instead of hanging forever.</t>
         </is>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E25)</f>
+        <f>SUM(E10:E26)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B25,"Must",E10:E25)</f>
+        <f>SUMIF(B10:B26,"Must",E10:E26)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B25,"Extra",E10:E25)</f>
+        <f>SUMIF(B10:B26,"Extra",E10:E26)</f>
         <v/>
       </c>
     </row>
@@ -1241,6 +1241,46 @@
       <c r="H25" s="6" t="inlineStr">
         <is>
           <t>The tool recognizes a Claude key and can send it real requests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PBI-18 Make it look nicer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PBI-18</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Add color, a spinner while the AI is thinking, and a real bordered results table</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The score is colored by how good it is, a spinner shows during real AI calls instead of a silent pause, and results appear in a proper table with the winner highlighted.</t>
         </is>
       </c>
     </row>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E26)</f>
+        <f>SUM(E10:E27)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B26,"Must",E10:E26)</f>
+        <f>SUMIF(B10:B27,"Must",E10:E27)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B26,"Extra",E10:E26)</f>
+        <f>SUMIF(B10:B27,"Extra",E10:E27)</f>
         <v/>
       </c>
     </row>
@@ -1281,6 +1281,46 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>The score is colored by how good it is, a spinner shows during real AI calls instead of a silent pause, and results appear in a proper table with the winner highlighted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PBI-19 Add a browser UI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PBI-19</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Run Improve and Compare from a page in your own browser instead of the terminal</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Typing 'prompteval web' opens a local page where typing a prompt (or 3 to compare) and clicking a button shows the same real score/ranking as the terminal.</t>
         </is>
       </c>
     </row>

--- a/Sprint_Tracker.xlsx
+++ b/Sprint_Tracker.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>SUM(E10:E27)</f>
+        <f>SUM(E10:E28)</f>
         <v/>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>SUMIF(B10:B27,"Must",E10:E27)</f>
+        <f>SUMIF(B10:B28,"Must",E10:E28)</f>
         <v/>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>SUMIF(B10:B27,"Extra",E10:E27)</f>
+        <f>SUMIF(B10:B28,"Extra",E10:E28)</f>
         <v/>
       </c>
     </row>
@@ -1321,6 +1321,46 @@
       <c r="H27" t="inlineStr">
         <is>
           <t>Typing 'prompteval web' opens a local page where typing a prompt (or 3 to compare) and clicking a button shows the same real score/ranking as the terminal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PBI-20 Save a history of past runs</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PBI-20</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Automatically save every browser-UI run to a local file so past results are never lost</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fri 7 Aug</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>A History tab lists every past Refine/Compare run; clicking one shows the full result again, and it survives closing the browser or restarting the server.</t>
         </is>
       </c>
     </row>
